--- a/Result/profitability/2371.xlsx
+++ b/Result/profitability/2371.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1887500000000001</v>
+        <v>-0.07874999999999988</v>
       </c>
       <c r="N2" t="n">
-        <v>17.12875</v>
+        <v>17.1025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1787499999999999</v>
+        <v>-0.4899999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>16.71875</v>
+        <v>16.685</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6437499999999999</v>
+        <v>-0.5412499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>14.465</v>
+        <v>14.33125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8637499999999998</v>
+        <v>-0.77125</v>
       </c>
       <c r="N5" t="n">
-        <v>8.6225</v>
+        <v>8.61125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.66</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9737499999999999</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35375</v>
+        <v>3.5125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.08</v>
+        <v>-0.22875</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.51</v>
+        <v>-0.35375</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.34875</v>
+        <v>-0.2225</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.25875</v>
+        <v>-2.142500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2371</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13014</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10753</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2261</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>684</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1519</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2203</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2825000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.14375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9299999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0565693430656935</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.363636363636363</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.005154639175257714</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
